--- a/hira_material_automation/output/monthly/202601_202608__acl_primary_fixation_metal__040023__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202608__acl_primary_fixation_metal__040023__normalized.xlsx
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-04T22:16:55</t>
+          <t>2026-08-14T21:28:55</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2489bd3f0801cd6cef7452965f2e5228db29e46199146dc4388c09088b6b810a</t>
+          <t>6a5b0c0dbc7aa31b83acb47293ce3a5fc998bf26bb34914499dd662348c50f58</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202608__acl_primary_fixation_metal__040023__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202608__acl_primary_fixation_metal__040023__normalized.xlsx
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-14T21:28:55</t>
+          <t>2026-08-24T21:34:03</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6a5b0c0dbc7aa31b83acb47293ce3a5fc998bf26bb34914499dd662348c50f58</t>
+          <t>932612ee7e8c8c38760670ac1bb22d4ed6e7c38a91a2f0200f6710503e8a984e</t>
         </is>
       </c>
     </row>
